--- a/output7/【河洛文讀注音-閩拼調符】《六國論》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調符】《六國論》.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BAC16FB-EE71-453C-86E6-4B2FEB6E8D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAA7214-8925-4059-B8BE-24764E498963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
@@ -10001,7 +10001,7 @@
       <c r="L55" s="48"/>
       <c r="M55" s="48"/>
       <c r="N55" s="48" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="O55" s="48"/>
       <c r="P55" s="48"/>
